--- a/dico.xlsx
+++ b/dico.xlsx
@@ -14,36 +14,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
-    <t>modeles</t>
+    <t>perimé</t>
   </si>
   <si>
-    <t>quantité</t>
-  </si>
-  <si>
-    <t>banane</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>citron</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>orange</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>pommes</t>
-  </si>
-  <si>
-    <t>8</t>
+    <t>reste</t>
   </si>
 </sst>
 </file>
@@ -375,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -387,35 +363,19 @@
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" t="s">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
         <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="A3">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
+      <c r="B3">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
